--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486820_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486820_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3676</v>
+        <v>5.2395</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2399</v>
+        <v>4.2609</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1276</v>
+        <v>0.9786</v>
       </c>
       <c r="G2" t="n">
         <v>5.1212</v>
@@ -610,13 +610,13 @@
         <v>3.2823</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3625</v>
+        <v>0.2344</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6818</v>
+        <v>0.7028</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3193</v>
+        <v>-0.4683</v>
       </c>
       <c r="V2" t="n">
         <v>1.6216</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5884</v>
+        <v>4.7208</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2013</v>
+        <v>1.4081</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3871</v>
+        <v>3.3126</v>
       </c>
       <c r="G3" t="n">
         <v>4.1309</v>
@@ -688,13 +688,13 @@
         <v>2.8962</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3458</v>
+        <v>-1.2134</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4418</v>
+        <v>-0.235</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.904</v>
+        <v>-0.9785</v>
       </c>
       <c r="V3" t="n">
         <v>0.06560000000000001</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.568</v>
+        <v>3.3778</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2238</v>
+        <v>2.8101</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3442</v>
+        <v>0.5677</v>
       </c>
       <c r="G4" t="n">
         <v>1.2775</v>
@@ -766,13 +766,13 @@
         <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.0965</v>
       </c>
       <c r="T4" t="n">
-        <v>0.882</v>
+        <v>0.4683</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7883</v>
+        <v>-0.5648</v>
       </c>
       <c r="V4" t="n">
         <v>0.266</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6281</v>
+        <v>2.6956</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7583</v>
+        <v>1.3788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8698</v>
+        <v>1.3167</v>
       </c>
       <c r="G5" t="n">
         <v>3.9915</v>
@@ -844,13 +844,13 @@
         <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.2673</v>
+        <v>-1.1998</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.214</v>
+        <v>-0.5935</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0533</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-1.4477</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6727</v>
+        <v>0.5955</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5466</v>
+        <v>-0.6982</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2192</v>
+        <v>1.2937</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4666</v>
@@ -922,13 +922,13 @@
         <v>2.8962</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1046</v>
+        <v>0.0274</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0546</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05</v>
+        <v>0.1245</v>
       </c>
       <c r="V6" t="n">
         <v>1.2277</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>G. CAMPOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6264</v>
+        <v>0.2207</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2085</v>
+        <v>1.5316</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8349</v>
+        <v>-1.3109</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9504</v>
+        <v>2.4208</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4484</v>
+        <v>0.1172</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5019</v>
+        <v>2.3036</v>
       </c>
       <c r="J7" t="n">
-        <v>0.044</v>
+        <v>1.5801</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2409</v>
+        <v>-0.2963</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2848</v>
+        <v>1.8764</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9943</v>
+        <v>0.8408</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2075</v>
+        <v>0.4135</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.4272</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7031</v>
+        <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0555</v>
+        <v>-0.131</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4142</v>
+        <v>-0.0485</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4696</v>
+        <v>-0.0825</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9421</v>
+        <v>-2.4554</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6565</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRÍGUEZ</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1889</v>
+        <v>0.0608</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2213</v>
+        <v>-2.1533</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4103</v>
+        <v>2.2141</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4208</v>
+        <v>-0.9504</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1172</v>
+        <v>-0.4484</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3036</v>
+        <v>-0.5019</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5801</v>
+        <v>0.044</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2963</v>
+        <v>-0.2409</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8764</v>
+        <v>0.2848</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8408</v>
+        <v>-0.9943</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4135</v>
+        <v>-0.2075</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4272</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3862</v>
+        <v>2.7031</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5405</v>
+        <v>-0.5101</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3587</v>
+        <v>-0.359</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1818</v>
+        <v>-0.1512</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4554</v>
+        <v>0.9421</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4554</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2345</v>
+        <v>-0.2983</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2781</v>
+        <v>-0.1808</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0436</v>
+        <v>-0.1175</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9273</v>
+        <v>-0.774</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1238</v>
+        <v>0.0896</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0511</v>
+        <v>-0.8636</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5285</v>
+        <v>0.1021</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3251</v>
+        <v>0.0207</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2035</v>
+        <v>0.0814</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6012</v>
+        <v>-0.8761</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4489</v>
+        <v>0.0689</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8477</v>
+        <v>-0.945</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7031</v>
+        <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1434</v>
+        <v>-0.2966</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4684</v>
+        <v>-0.2829</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.325</v>
+        <v>-0.0137</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9191</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8142</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4762</v>
+        <v>-0.6675</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2842</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.192</v>
+        <v>-0.0309</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.774</v>
+        <v>0.9273</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0896</v>
+        <v>-0.1238</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8636</v>
+        <v>1.0511</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1021</v>
+        <v>1.5285</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0207</v>
+        <v>1.3251</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0814</v>
+        <v>0.2035</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8761</v>
+        <v>-0.6012</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0689</v>
+        <v>-1.4489</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.945</v>
+        <v>0.8477</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7723</v>
+        <v>2.7031</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4745</v>
+        <v>-0.2896</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3863</v>
+        <v>0.1099</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0882</v>
+        <v>-0.3995</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.9191</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8142</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7333</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.9472</v>
+        <v>-9.0647</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0288</v>
+        <v>-5.1463</v>
       </c>
       <c r="F11" t="n">
         <v>-3.9184</v>
@@ -1312,10 +1312,10 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.993</v>
+        <v>-0.1105</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1036</v>
+        <v>-0.2211</v>
       </c>
       <c r="U11" t="n">
         <v>0.1106</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.6044</v>
+        <v>6.8802</v>
       </c>
       <c r="E12" t="n">
-        <v>2.298399999999999</v>
+        <v>2.574300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>4.3057</v>
+        <v>4.305699999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>7.827799999999997</v>
+        <v>7.827799999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-1.0337</v>
@@ -1375,13 +1375,13 @@
         <v>-4.9086</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.937099999999999</v>
+        <v>-7.937100000000001</v>
       </c>
       <c r="O12" t="n">
         <v>3.0284</v>
       </c>
       <c r="P12" t="n">
-        <v>5.792199999999999</v>
+        <v>5.7922</v>
       </c>
       <c r="Q12" t="n">
         <v>-15.4462</v>
@@ -1390,13 +1390,13 @@
         <v>21.2386</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.8614</v>
+        <v>-3.5857</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8318</v>
+        <v>-0.5560999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.0297</v>
+        <v>-3.029800000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1546</v>
@@ -1405,7 +1405,7 @@
         <v>5.8401</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.9946</v>
+        <v>-8.994600000000002</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.681</v>
+        <v>2.5983</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5435</v>
+        <v>1.3367</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1374</v>
+        <v>1.2616</v>
       </c>
       <c r="G13" t="n">
         <v>1.5778</v>
@@ -1468,13 +1468,13 @@
         <v>0.7723</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3309</v>
+        <v>0.2482</v>
       </c>
       <c r="T13" t="n">
-        <v>0.248</v>
+        <v>0.0412</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0829</v>
+        <v>0.2071</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7478</v>
+        <v>0.5079</v>
       </c>
       <c r="E14" t="n">
-        <v>1.143</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3952</v>
+        <v>-0.2214</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6232</v>
@@ -1546,13 +1546,13 @@
         <v>0.7723</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3364</v>
+        <v>0.0965</v>
       </c>
       <c r="T14" t="n">
-        <v>0.772</v>
+        <v>0.3583</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4356</v>
+        <v>-0.2618</v>
       </c>
       <c r="V14" t="n">
         <v>1.2277</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DELICADO DOMINGUEZ</t>
+          <t>P. RODRIGUEZ PASCUAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6561</v>
+        <v>0.25</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9916</v>
+        <v>1.7997</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3355</v>
+        <v>-1.5497</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4139</v>
+        <v>-0.8329</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3584</v>
+        <v>-1.1517</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7723</v>
+        <v>0.3188</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6705</v>
+        <v>1.8522</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3938</v>
+        <v>0.091</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7233000000000001</v>
+        <v>1.7612</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0844</v>
+        <v>-2.6851</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0354</v>
+        <v>-1.2426</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.049</v>
+        <v>-1.4424</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5446</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8616</v>
+        <v>-2.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3169</v>
+        <v>2.7031</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7578</v>
+        <v>0.0483</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8125</v>
+        <v>0.1027</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0547</v>
+        <v>-0.0544</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8568</v>
+        <v>1.2277</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3701</v>
+        <v>2.741</v>
       </c>
       <c r="X15" t="n">
         <v>-1.5133</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2013</v>
+        <v>-0.298</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7305</v>
+        <v>-1.1442</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9317</v>
+        <v>0.8461</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1408</v>
@@ -1702,13 +1702,13 @@
         <v>2.8962</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6164</v>
+        <v>1.1171</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1576</v>
+        <v>0.7439</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4587</v>
+        <v>0.3731</v>
       </c>
       <c r="V16" t="n">
         <v>0.6565</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PASCUAL</t>
+          <t>A. DELICADO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9937</v>
+        <v>-0.7159</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0415</v>
+        <v>0.2334</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0352</v>
+        <v>-0.9493</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8329</v>
+        <v>-1.4139</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1517</v>
+        <v>0.3584</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3188</v>
+        <v>-1.7723</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8522</v>
+        <v>0.6705</v>
       </c>
       <c r="K17" t="n">
-        <v>0.091</v>
+        <v>1.3938</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7612</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6851</v>
+        <v>-2.0844</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2426</v>
+        <v>-1.0354</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4424</v>
+        <v>-1.049</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1931</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>-3.8616</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7031</v>
+        <v>2.3169</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1954</v>
+        <v>1.3858</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6555</v>
+        <v>1.0543</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.54</v>
+        <v>0.3315</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2277</v>
+        <v>0.8568</v>
       </c>
       <c r="W17" t="n">
-        <v>2.741</v>
+        <v>2.3701</v>
       </c>
       <c r="X17" t="n">
         <v>-1.5133</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0498</v>
+        <v>-1.2306</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0299</v>
+        <v>-1.4093</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.02</v>
+        <v>0.1787</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8307</v>
@@ -1858,13 +1858,13 @@
         <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.833</v>
+        <v>-0.0138</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5518</v>
+        <v>0.0687</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2811</v>
+        <v>-0.0825</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0838</v>
+        <v>-3.1624</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3796</v>
+        <v>-2.0002</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-1.1622</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6878</v>
@@ -1936,13 +1936,13 @@
         <v>2.8962</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3337</v>
+        <v>1.2551</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1576</v>
+        <v>0.5371</v>
       </c>
       <c r="U19" t="n">
-        <v>1.176</v>
+        <v>0.718</v>
       </c>
       <c r="V19" t="n">
         <v>-1.7989</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.763</v>
+        <v>-3.8641</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8853</v>
+        <v>-3.8511</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1223</v>
+        <v>-0.013</v>
       </c>
       <c r="G20" t="n">
         <v>-4.8764</v>
@@ -2014,13 +2014,13 @@
         <v>2.51</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4852</v>
+        <v>0.4138</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9108000000000001</v>
+        <v>0.1234</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4256</v>
+        <v>0.2904</v>
       </c>
       <c r="V20" t="n">
         <v>0.9847</v>
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.6041</v>
+        <v>-5.914800000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3057</v>
+        <v>-4.305700000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2986</v>
+        <v>-1.6092</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.8279</v>
+        <v>-7.827900000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.033700000000001</v>
+        <v>1.0337</v>
       </c>
       <c r="I21" t="n">
         <v>-8.861699999999999</v>
@@ -2077,7 +2077,7 @@
         <v>-12.7366</v>
       </c>
       <c r="N21" t="n">
-        <v>-6.9033</v>
+        <v>-6.903300000000001</v>
       </c>
       <c r="O21" t="n">
         <v>-5.833</v>
@@ -2092,19 +2092,19 @@
         <v>15.4462</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8616</v>
+        <v>4.551</v>
       </c>
       <c r="T21" t="n">
         <v>3.0296</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8317999999999999</v>
+        <v>1.5214</v>
       </c>
       <c r="V21" t="n">
         <v>3.1545</v>
       </c>
       <c r="W21" t="n">
-        <v>8.994499999999999</v>
+        <v>8.9945</v>
       </c>
       <c r="X21" t="n">
         <v>-5.840100000000001</v>
